--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89592343</v>
+        <v>93855905</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471391.0158327154</v>
+        <v>471302</v>
       </c>
       <c r="R2" t="n">
-        <v>7141923.006695494</v>
+        <v>7141710</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,69 +771,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89592341</v>
+        <v>128052663</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>824</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471235.0982151624</v>
+        <v>471510</v>
       </c>
       <c r="R3" t="n">
-        <v>7141830.17100752</v>
+        <v>7141973</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,57 +867,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Örtrik och bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89592266</v>
+        <v>89592343</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471260.0941539817</v>
+        <v>471391</v>
       </c>
       <c r="R4" t="n">
-        <v>7141816.959593153</v>
+        <v>7141923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +956,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89592253</v>
+        <v>16849565</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1024,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471247.9398948489</v>
+        <v>471617</v>
       </c>
       <c r="R5" t="n">
-        <v>7141814.045750679</v>
+        <v>7141807</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,21 +1070,34 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Niina Sallmén, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1106,7 @@
         <v>89592270</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471260.9886947797</v>
+        <v>471261</v>
       </c>
       <c r="R6" t="n">
-        <v>7141819.9791142</v>
+        <v>7141820</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1171,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89592246</v>
+        <v>89592276</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471436.1520565019</v>
+        <v>471386</v>
       </c>
       <c r="R7" t="n">
-        <v>7141608.10973258</v>
+        <v>7141922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1272,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1305,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89592306</v>
+        <v>89592284</v>
       </c>
       <c r="B8" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471304.039839308</v>
+        <v>471290</v>
       </c>
       <c r="R8" t="n">
-        <v>7142115.864073517</v>
+        <v>7142126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1373,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1406,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89592353</v>
+        <v>89592294</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471288.9488978228</v>
+        <v>471358</v>
       </c>
       <c r="R9" t="n">
-        <v>7142122.925788428</v>
+        <v>7142080</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1474,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89592276</v>
+        <v>89592322</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471385.8111441133</v>
+        <v>471428</v>
       </c>
       <c r="R10" t="n">
-        <v>7141922.190230086</v>
+        <v>7141774</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1575,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89592293</v>
+        <v>89592349</v>
       </c>
       <c r="B11" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471428.1693592006</v>
+        <v>471434</v>
       </c>
       <c r="R11" t="n">
-        <v>7141773.861077032</v>
+        <v>7141824</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1676,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89592344</v>
+        <v>115383067</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,34 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471335.8645165892</v>
+        <v>471298</v>
       </c>
       <c r="R12" t="n">
-        <v>7141860.802819101</v>
+        <v>7142137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,22 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,73 +1790,71 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89592319</v>
+        <v>93856083</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471289.8433242105</v>
+        <v>471512</v>
       </c>
       <c r="R13" t="n">
-        <v>7142125.945015683</v>
+        <v>7141687</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,22 +1878,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,31 +1908,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89592294</v>
+        <v>128052689</v>
       </c>
       <c r="B14" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,37 +1931,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>3277</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471357.836076637</v>
+        <v>471513</v>
       </c>
       <c r="R14" t="n">
-        <v>7142079.893837737</v>
+        <v>7141968</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2137,22 +1988,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,57 +2004,53 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Örtrik och bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89592274</v>
+        <v>89592253</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471395.0183180806</v>
+        <v>471248</v>
       </c>
       <c r="R15" t="n">
-        <v>7141934.215437451</v>
+        <v>7141814</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,21 +2093,11 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2279,11 +2106,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2304,37 +2126,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89592284</v>
+        <v>89592262</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471289.8433242105</v>
+        <v>471312</v>
       </c>
       <c r="R16" t="n">
-        <v>7142125.945015683</v>
+        <v>7142019</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,19 +2194,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,37 +2227,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89592285</v>
+        <v>89592306</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471428.1693592006</v>
+        <v>471304</v>
       </c>
       <c r="R17" t="n">
-        <v>7141773.861077032</v>
+        <v>7142116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2493,19 +2295,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,15 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89592322</v>
+        <v>89592285</v>
       </c>
       <c r="B18" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2576,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471428.1693592006</v>
+        <v>471428</v>
       </c>
       <c r="R18" t="n">
-        <v>7141773.861077032</v>
+        <v>7141774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,19 +2396,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,15 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89592262</v>
+        <v>89592319</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2692,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471311.7928036463</v>
+        <v>471290</v>
       </c>
       <c r="R19" t="n">
-        <v>7142018.906040798</v>
+        <v>7142126</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2725,19 +2497,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,15 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89592349</v>
+        <v>89592344</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2808,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471433.8341779427</v>
+        <v>471336</v>
       </c>
       <c r="R20" t="n">
-        <v>7141823.98537496</v>
+        <v>7141861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,19 +2598,9 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,15 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89592336</v>
+        <v>115377345</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2900,34 +2642,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471340.9641956232</v>
+        <v>471298</v>
       </c>
       <c r="R21" t="n">
-        <v>7142128.061271969</v>
+        <v>7142137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,27 +2705,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,35 +2721,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>93855905</v>
+        <v>115379346</v>
       </c>
       <c r="B22" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3021,38 +2753,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471302.8328109484</v>
+        <v>471362</v>
       </c>
       <c r="R22" t="n">
-        <v>7141709.71480848</v>
+        <v>7141895</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3076,22 +2807,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3102,71 +2823,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>93856083</v>
+        <v>115380107</v>
       </c>
       <c r="B23" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471511.8217831923</v>
+        <v>471616</v>
       </c>
       <c r="R23" t="n">
-        <v>7141687.432804757</v>
+        <v>7141881</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3190,22 +2909,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,31 +2925,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115380448</v>
+        <v>115380340</v>
       </c>
       <c r="B24" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,21 +2957,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3272,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471496</v>
+        <v>471461</v>
       </c>
       <c r="R24" t="n">
-        <v>7141820</v>
+        <v>7141651</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3318,6 +3027,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3334,53 +3048,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115379346</v>
+        <v>89592266</v>
       </c>
       <c r="B25" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471362</v>
+        <v>471260</v>
       </c>
       <c r="R25" t="n">
-        <v>7141895</v>
+        <v>7141817</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3404,12 +3113,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,74 +3129,68 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115380340</v>
+        <v>89592274</v>
       </c>
       <c r="B26" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471461</v>
+        <v>471395</v>
       </c>
       <c r="R26" t="n">
-        <v>7141651</v>
+        <v>7141934</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,12 +3214,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,70 +3231,69 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115383067</v>
+        <v>89592341</v>
       </c>
       <c r="B27" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471298</v>
+        <v>471235</v>
       </c>
       <c r="R27" t="n">
-        <v>7142137</v>
+        <v>7141830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3618,12 +3320,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,74 +3336,68 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115380107</v>
+        <v>89592353</v>
       </c>
       <c r="B28" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471616</v>
+        <v>471289</v>
       </c>
       <c r="R28" t="n">
-        <v>7141881</v>
+        <v>7142123</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3725,12 +3421,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3741,36 +3437,30 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115377345</v>
+        <v>89592336</v>
       </c>
       <c r="B29" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,43 +3468,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471298</v>
+        <v>471341</v>
       </c>
       <c r="R29" t="n">
-        <v>7142137</v>
+        <v>7142128</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,12 +3522,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3857,31 +3543,30 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128052689</v>
+        <v>115380448</v>
       </c>
       <c r="B30" t="n">
-        <v>91584</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3889,40 +3574,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3277</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471513</v>
+        <v>471496</v>
       </c>
       <c r="R30" t="n">
-        <v>7141968</v>
+        <v>7141820</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3946,12 +3628,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,72 +3644,64 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Örtrik och bördig grannaturskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128052663</v>
+        <v>89592246</v>
       </c>
       <c r="B31" t="n">
-        <v>88733</v>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>824</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471510</v>
+        <v>471436</v>
       </c>
       <c r="R31" t="n">
-        <v>7141973</v>
+        <v>7141608</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4051,12 +3725,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,24 +3741,124 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Örtrik och bördig grannaturskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>89592293</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>471428</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7141774</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93855905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128052663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592343</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16849565</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592270</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592276</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592284</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592294</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592322</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592349</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383067</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93856083</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128052689</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2123,6 +2193,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592253</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2224,6 +2299,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592262</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592306</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2426,6 +2511,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592285</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592319</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2628,6 +2723,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592344</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2739,6 +2839,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115377345</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115379346</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2943,6 +3053,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115380107</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3045,6 +3160,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115380340</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3146,6 +3266,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592266</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3252,6 +3377,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592274</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3353,6 +3483,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592341</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3454,6 +3589,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592353</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3560,6 +3700,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592336</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3657,6 +3802,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115380448</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3758,6 +3908,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592246</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3859,8 +4014,46 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,51 +793,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128052663</v>
+        <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>89155</v>
+        <v>83423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>824</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
+          <t>Kalberget mitten, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471510</v>
+        <v>471363</v>
       </c>
       <c r="R3" t="n">
-        <v>7141973</v>
+        <v>7141936</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,74 +884,72 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Örtrik och bördig grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf</t>
+          <t>Linnea Ingelsbo, Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128052663</t>
+          <t>https://artportalen.se/Sighting/136196763</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89592343</v>
+        <v>128052663</v>
       </c>
       <c r="B4" t="n">
-        <v>91905</v>
+        <v>89155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>824</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471391</v>
+        <v>471510</v>
       </c>
       <c r="R4" t="n">
-        <v>7141923</v>
+        <v>7141973</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,12 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,57 +989,58 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Örtrik och bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592343</t>
+          <t>https://artportalen.se/Sighting/128052663</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16849565</v>
+        <v>89592343</v>
       </c>
       <c r="B5" t="n">
-        <v>79486</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471617</v>
+        <v>471391</v>
       </c>
       <c r="R5" t="n">
-        <v>7141807</v>
+        <v>7141923</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-06-27</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-06-27</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,48 +1096,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16849565</t>
+          <t>https://artportalen.se/Sighting/89592343</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89592270</v>
+        <v>136202475</v>
       </c>
       <c r="B6" t="n">
-        <v>80433</v>
+        <v>92061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1132,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471261</v>
+        <v>471274</v>
       </c>
       <c r="R6" t="n">
-        <v>7141820</v>
+        <v>7141879</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1186,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,56 +1203,57 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592270</t>
+          <t>https://artportalen.se/Sighting/136202475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89592276</v>
+        <v>16849565</v>
       </c>
       <c r="B7" t="n">
-        <v>80433</v>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471386</v>
+        <v>471617</v>
       </c>
       <c r="R7" t="n">
-        <v>7141922</v>
+        <v>7141807</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,12 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2014-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2014-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,73 +1309,86 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Niina Sallmén, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592276</t>
+          <t>https://artportalen.se/Sighting/16849565</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89592284</v>
+        <v>136202467</v>
       </c>
       <c r="B8" t="n">
-        <v>80433</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471290</v>
+        <v>471593</v>
       </c>
       <c r="R8" t="n">
-        <v>7142126</v>
+        <v>7141934</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,12 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,72 +1429,73 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592284</t>
+          <t>https://artportalen.se/Sighting/136202467</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89592294</v>
+        <v>136196766</v>
       </c>
       <c r="B9" t="n">
-        <v>80433</v>
+        <v>75527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget mitten, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471358</v>
+        <v>471197</v>
       </c>
       <c r="R9" t="n">
-        <v>7142080</v>
+        <v>7141805</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,12 +1519,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,28 +1549,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linnea Ingelsbo, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592294</t>
+          <t>https://artportalen.se/Sighting/136196766</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89592322</v>
+        <v>89592270</v>
       </c>
       <c r="B10" t="n">
         <v>80433</v>
@@ -1587,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471428</v>
+        <v>471261</v>
       </c>
       <c r="R10" t="n">
-        <v>7141774</v>
+        <v>7141820</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,13 +1666,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592322</t>
+          <t>https://artportalen.se/Sighting/89592270</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89592349</v>
+        <v>89592276</v>
       </c>
       <c r="B11" t="n">
         <v>80433</v>
@@ -1693,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471434</v>
+        <v>471386</v>
       </c>
       <c r="R11" t="n">
-        <v>7141824</v>
+        <v>7141922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,13 +1772,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592349</t>
+          <t>https://artportalen.se/Sighting/89592276</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115383067</v>
+        <v>89592284</v>
       </c>
       <c r="B12" t="n">
         <v>80433</v>
@@ -1795,14 +1809,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471298</v>
+        <v>471290</v>
       </c>
       <c r="R12" t="n">
-        <v>7142137</v>
+        <v>7142126</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,12 +1843,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,76 +1859,73 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115383067</t>
+          <t>https://artportalen.se/Sighting/89592284</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>93856083</v>
+        <v>89592294</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471512</v>
+        <v>471358</v>
       </c>
       <c r="R13" t="n">
-        <v>7141687</v>
+        <v>7142080</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,22 +1949,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,27 +1969,31 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93856083</t>
+          <t>https://artportalen.se/Sighting/89592294</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128052689</v>
+        <v>89592322</v>
       </c>
       <c r="B14" t="n">
-        <v>92037</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,40 +2001,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3277</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471513</v>
+        <v>471428</v>
       </c>
       <c r="R14" t="n">
-        <v>7141968</v>
+        <v>7141774</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,12 +2055,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,58 +2071,57 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Örtrik och bördig grannaturskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128052689</t>
+          <t>https://artportalen.se/Sighting/89592322</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89592253</v>
+        <v>89592349</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471248</v>
+        <v>471434</v>
       </c>
       <c r="R15" t="n">
-        <v>7141814</v>
+        <v>7141824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,51 +2196,51 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592253</t>
+          <t>https://artportalen.se/Sighting/89592349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89592262</v>
+        <v>115383067</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471312</v>
+        <v>471298</v>
       </c>
       <c r="R16" t="n">
-        <v>7142019</v>
+        <v>7142137</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,12 +2267,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,73 +2283,74 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592262</t>
+          <t>https://artportalen.se/Sighting/115383067</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89592306</v>
+        <v>136202472</v>
       </c>
       <c r="B17" t="n">
-        <v>83290</v>
+        <v>80560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471304</v>
+        <v>471488</v>
       </c>
       <c r="R17" t="n">
-        <v>7142116</v>
+        <v>7141876</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2372,12 +2374,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,34 +2391,35 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592306</t>
+          <t>https://artportalen.se/Sighting/136202472</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89592285</v>
+        <v>136202478</v>
       </c>
       <c r="B18" t="n">
-        <v>80432</v>
+        <v>80560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,37 +2427,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471428</v>
+        <v>471221</v>
       </c>
       <c r="R18" t="n">
-        <v>7141774</v>
+        <v>7141862</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2478,12 +2481,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,72 +2498,75 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592285</t>
+          <t>https://artportalen.se/Sighting/136202478</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89592319</v>
+        <v>93856083</v>
       </c>
       <c r="B19" t="n">
-        <v>80432</v>
+        <v>96348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471290</v>
+        <v>471512</v>
       </c>
       <c r="R19" t="n">
-        <v>7142126</v>
+        <v>7141687</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,12 +2590,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,31 +2620,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592319</t>
+          <t>https://artportalen.se/Sighting/93856083</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89592344</v>
+        <v>128052689</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>92037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,37 +2648,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>3277</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471336</v>
+        <v>471513</v>
       </c>
       <c r="R20" t="n">
-        <v>7141861</v>
+        <v>7141968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,12 +2705,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,79 +2721,71 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Örtrik och bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592344</t>
+          <t>https://artportalen.se/Sighting/128052689</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115377345</v>
+        <v>89592253</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471298</v>
+        <v>471248</v>
       </c>
       <c r="R21" t="n">
-        <v>7142137</v>
+        <v>7141814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,12 +2812,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,74 +2828,73 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377345</t>
+          <t>https://artportalen.se/Sighting/89592253</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115379346</v>
+        <v>89592262</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471362</v>
+        <v>471312</v>
       </c>
       <c r="R22" t="n">
-        <v>7141895</v>
+        <v>7142019</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,12 +2918,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2928,74 +2934,73 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115379346</t>
+          <t>https://artportalen.se/Sighting/89592262</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115380107</v>
+        <v>136202476</v>
       </c>
       <c r="B23" t="n">
-        <v>80432</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471616</v>
+        <v>471273</v>
       </c>
       <c r="R23" t="n">
         <v>7141881</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3019,12 +3024,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,73 +3041,73 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
+      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115380107</t>
+          <t>https://artportalen.se/Sighting/136202476</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115380340</v>
+        <v>89592306</v>
       </c>
       <c r="B24" t="n">
-        <v>80432</v>
+        <v>83290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471461</v>
+        <v>471304</v>
       </c>
       <c r="R24" t="n">
-        <v>7141651</v>
+        <v>7142116</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3126,12 +3131,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,58 +3147,57 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115380340</t>
+          <t>https://artportalen.se/Sighting/89592306</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89592266</v>
+        <v>89592285</v>
       </c>
       <c r="B25" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3203,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471260</v>
+        <v>471428</v>
       </c>
       <c r="R25" t="n">
-        <v>7141817</v>
+        <v>7141774</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,38 +3272,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592266</t>
+          <t>https://artportalen.se/Sighting/89592285</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89592274</v>
+        <v>89592319</v>
       </c>
       <c r="B26" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3309,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471395</v>
+        <v>471290</v>
       </c>
       <c r="R26" t="n">
-        <v>7141934</v>
+        <v>7142126</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,11 +3360,6 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3379,38 +3378,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592274</t>
+          <t>https://artportalen.se/Sighting/89592319</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89592341</v>
+        <v>89592344</v>
       </c>
       <c r="B27" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3420,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471235</v>
+        <v>471336</v>
       </c>
       <c r="R27" t="n">
-        <v>7141830</v>
+        <v>7141861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,51 +3484,60 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592341</t>
+          <t>https://artportalen.se/Sighting/89592344</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89592353</v>
+        <v>115377345</v>
       </c>
       <c r="B28" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471289</v>
+        <v>471298</v>
       </c>
       <c r="R28" t="n">
-        <v>7142123</v>
+        <v>7142137</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3556,12 +3564,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,35 +3580,36 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592353</t>
+          <t>https://artportalen.se/Sighting/115377345</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89592336</v>
+        <v>115379346</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,37 +3617,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471341</v>
+        <v>471362</v>
       </c>
       <c r="R29" t="n">
-        <v>7142128</v>
+        <v>7141895</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3662,17 +3671,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3683,35 +3687,36 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592336</t>
+          <t>https://artportalen.se/Sighting/115379346</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115380448</v>
+        <v>115380107</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3719,21 +3724,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3743,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471496</v>
+        <v>471616</v>
       </c>
       <c r="R30" t="n">
-        <v>7141820</v>
+        <v>7141881</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3790,6 +3795,11 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -3804,54 +3814,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115380448</t>
+          <t>https://artportalen.se/Sighting/115380107</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89592246</v>
+        <v>115380340</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471436</v>
+        <v>471461</v>
       </c>
       <c r="R31" t="n">
-        <v>7141608</v>
+        <v>7141651</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3875,12 +3885,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3891,73 +3901,74 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592246</t>
+          <t>https://artportalen.se/Sighting/115380340</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89592293</v>
+        <v>136202477</v>
       </c>
       <c r="B32" t="n">
-        <v>80398</v>
+        <v>80559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471428</v>
+        <v>471221</v>
       </c>
       <c r="R32" t="n">
-        <v>7141774</v>
+        <v>7142065</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3981,12 +3992,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,25 +4009,988 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AR32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136202477</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>89592266</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>471260</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7141817</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592266</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>89592274</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>471395</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7141934</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592274</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>89592341</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>471235</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7141830</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592341</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>89592353</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>471289</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7142123</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592353</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>89592336</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>471341</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7142128</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592336</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115380448</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Klingerhögtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>471496</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7141820</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115380448</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>89592246</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>471436</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7141608</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592246</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>89592293</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>471428</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7141774</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89592293</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136196765</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79916</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6038705</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cliostomum piceicola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalberget mitten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>471210</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7141812</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo, Johan Råghall, Rashid Kadhim, Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136196765</t>
         </is>
       </c>
     </row>
@@ -4053,6 +5027,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136202475</v>
+        <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471274</v>
+        <v>471370</v>
       </c>
       <c r="R6" t="n">
-        <v>7141879</v>
+        <v>7141564</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1189,21 @@
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1203,73 +1213,68 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202475</t>
+          <t>https://artportalen.se/Sighting/136195679</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16849565</v>
+        <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>79486</v>
+        <v>92062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471617</v>
+        <v>471274</v>
       </c>
       <c r="R7" t="n">
-        <v>7141807</v>
+        <v>7141879</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-06-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-06-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,47 +1315,35 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran</t>
-        </is>
-      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16849565</t>
+          <t>https://artportalen.se/Sighting/136202475</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136202467</v>
+        <v>16849565</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,17 +1371,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471593</v>
+        <v>471617</v>
       </c>
       <c r="R8" t="n">
-        <v>7141934</v>
+        <v>7141807</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,12 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2014-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2014-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,35 +1422,47 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gran</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+          <t>Niina Sallmén, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>SMF:s mykologivecka</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202467</t>
+          <t>https://artportalen.se/Sighting/16849565</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136196766</v>
+        <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>75527</v>
+        <v>79603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,37 +1470,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1776</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalberget mitten, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471197</v>
+        <v>471593</v>
       </c>
       <c r="R9" t="n">
-        <v>7141805</v>
+        <v>7141934</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,21 +1527,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1546,68 +1541,73 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136196766</t>
+          <t>https://artportalen.se/Sighting/136202467</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89592270</v>
+        <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>80433</v>
+        <v>75527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget mitten, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471261</v>
+        <v>471197</v>
       </c>
       <c r="R10" t="n">
-        <v>7141820</v>
+        <v>7141805</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,12 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,28 +1661,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linnea Ingelsbo, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592270</t>
+          <t>https://artportalen.se/Sighting/136196766</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89592276</v>
+        <v>89592270</v>
       </c>
       <c r="B11" t="n">
         <v>80433</v>
@@ -1707,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471386</v>
+        <v>471261</v>
       </c>
       <c r="R11" t="n">
-        <v>7141922</v>
+        <v>7141820</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,13 +1778,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592276</t>
+          <t>https://artportalen.se/Sighting/89592270</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89592284</v>
+        <v>89592276</v>
       </c>
       <c r="B12" t="n">
         <v>80433</v>
@@ -1813,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471290</v>
+        <v>471386</v>
       </c>
       <c r="R12" t="n">
-        <v>7142126</v>
+        <v>7141922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,13 +1884,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592284</t>
+          <t>https://artportalen.se/Sighting/89592276</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89592294</v>
+        <v>89592284</v>
       </c>
       <c r="B13" t="n">
         <v>80433</v>
@@ -1919,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471358</v>
+        <v>471290</v>
       </c>
       <c r="R13" t="n">
-        <v>7142080</v>
+        <v>7142126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,13 +1990,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592294</t>
+          <t>https://artportalen.se/Sighting/89592284</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89592322</v>
+        <v>89592294</v>
       </c>
       <c r="B14" t="n">
         <v>80433</v>
@@ -2025,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471428</v>
+        <v>471358</v>
       </c>
       <c r="R14" t="n">
-        <v>7141774</v>
+        <v>7142080</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,13 +2096,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592322</t>
+          <t>https://artportalen.se/Sighting/89592294</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89592349</v>
+        <v>89592322</v>
       </c>
       <c r="B15" t="n">
         <v>80433</v>
@@ -2131,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471434</v>
+        <v>471428</v>
       </c>
       <c r="R15" t="n">
-        <v>7141824</v>
+        <v>7141774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,13 +2202,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592349</t>
+          <t>https://artportalen.se/Sighting/89592322</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115383067</v>
+        <v>89592349</v>
       </c>
       <c r="B16" t="n">
         <v>80433</v>
@@ -2233,14 +2239,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471298</v>
+        <v>471434</v>
       </c>
       <c r="R16" t="n">
-        <v>7142137</v>
+        <v>7141824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,12 +2273,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,36 +2289,35 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115383067</t>
+          <t>https://artportalen.se/Sighting/89592349</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136202472</v>
+        <v>115383067</v>
       </c>
       <c r="B17" t="n">
-        <v>80560</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,17 +2345,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471488</v>
+        <v>471298</v>
       </c>
       <c r="R17" t="n">
-        <v>7141876</v>
+        <v>7142137</v>
       </c>
       <c r="S17" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2374,12 +2379,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,32 +2396,32 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AR17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202472</t>
+          <t>https://artportalen.se/Sighting/115383067</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136202478</v>
+        <v>136195682</v>
       </c>
       <c r="B18" t="n">
         <v>80560</v>
@@ -2451,13 +2456,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471221</v>
+        <v>471500</v>
       </c>
       <c r="R18" t="n">
-        <v>7141862</v>
+        <v>7141903</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2484,11 +2489,21 @@
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2498,75 +2513,68 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202478</t>
+          <t>https://artportalen.se/Sighting/136195682</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>93856083</v>
+        <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
+        <v>80560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471512</v>
+        <v>471488</v>
       </c>
       <c r="R19" t="n">
-        <v>7141687</v>
+        <v>7141876</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2590,22 +2598,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,30 +2615,35 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AR19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93856083</t>
+          <t>https://artportalen.se/Sighting/136202472</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128052689</v>
+        <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>92037</v>
+        <v>80560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,40 +2651,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3277</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471513</v>
+        <v>471221</v>
       </c>
       <c r="R20" t="n">
-        <v>7141968</v>
+        <v>7141862</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,73 +2722,75 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Örtrik och bördig grannaturskog</t>
-        </is>
-      </c>
+      <c r="AR20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128052689</t>
+          <t>https://artportalen.se/Sighting/136202478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89592253</v>
+        <v>93856083</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>96348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471248</v>
+        <v>471512</v>
       </c>
       <c r="R21" t="n">
-        <v>7141814</v>
+        <v>7141687</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2812,12 +2814,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2832,69 +2844,68 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592253</t>
+          <t>https://artportalen.se/Sighting/93856083</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89592262</v>
+        <v>128052689</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>92037</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471312</v>
+        <v>471513</v>
       </c>
       <c r="R22" t="n">
-        <v>7142019</v>
+        <v>7141968</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2918,12 +2929,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,35 +2945,36 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Örtrik och bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592262</t>
+          <t>https://artportalen.se/Sighting/128052689</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136202476</v>
+        <v>89592253</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2990,17 +3002,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471273</v>
+        <v>471248</v>
       </c>
       <c r="R23" t="n">
-        <v>7141881</v>
+        <v>7141814</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,12 +3036,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,57 +3053,56 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>SMF:s mykologivecka</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202476</t>
+          <t>https://artportalen.se/Sighting/89592253</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89592306</v>
+        <v>89592262</v>
       </c>
       <c r="B24" t="n">
-        <v>83290</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3101,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471304</v>
+        <v>471312</v>
       </c>
       <c r="R24" t="n">
-        <v>7142116</v>
+        <v>7142019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,54 +3177,54 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592306</t>
+          <t>https://artportalen.se/Sighting/89592262</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89592285</v>
+        <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>80432</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471428</v>
+        <v>471273</v>
       </c>
       <c r="R25" t="n">
-        <v>7141774</v>
+        <v>7141881</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3237,12 +3248,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,56 +3265,57 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AR25" t="inlineStr"/>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592285</t>
+          <t>https://artportalen.se/Sighting/136202476</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89592319</v>
+        <v>89592306</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>83290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471290</v>
+        <v>471304</v>
       </c>
       <c r="R26" t="n">
-        <v>7142126</v>
+        <v>7142116</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,13 +3390,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592319</t>
+          <t>https://artportalen.se/Sighting/89592306</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89592344</v>
+        <v>89592285</v>
       </c>
       <c r="B27" t="n">
         <v>80432</v>
@@ -3419,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471336</v>
+        <v>471428</v>
       </c>
       <c r="R27" t="n">
-        <v>7141861</v>
+        <v>7141774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,13 +3496,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592344</t>
+          <t>https://artportalen.se/Sighting/89592285</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115377345</v>
+        <v>89592319</v>
       </c>
       <c r="B28" t="n">
         <v>80432</v>
@@ -3518,26 +3530,17 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471298</v>
+        <v>471290</v>
       </c>
       <c r="R28" t="n">
-        <v>7142137</v>
+        <v>7142126</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,12 +3567,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,33 +3583,32 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377345</t>
+          <t>https://artportalen.se/Sighting/89592319</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115379346</v>
+        <v>89592344</v>
       </c>
       <c r="B29" t="n">
         <v>80432</v>
@@ -3637,17 +3639,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471362</v>
+        <v>471336</v>
       </c>
       <c r="R29" t="n">
-        <v>7141895</v>
+        <v>7141861</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3671,12 +3673,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3687,33 +3689,32 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115379346</t>
+          <t>https://artportalen.se/Sighting/89592344</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115380107</v>
+        <v>115377345</v>
       </c>
       <c r="B30" t="n">
         <v>80432</v>
@@ -3741,20 +3742,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471616</v>
+        <v>471298</v>
       </c>
       <c r="R30" t="n">
-        <v>7141881</v>
+        <v>7142137</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3814,13 +3824,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115380107</t>
+          <t>https://artportalen.se/Sighting/115377345</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115380340</v>
+        <v>115379346</v>
       </c>
       <c r="B31" t="n">
         <v>80432</v>
@@ -3855,13 +3865,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471461</v>
+        <v>471362</v>
       </c>
       <c r="R31" t="n">
-        <v>7141651</v>
+        <v>7141895</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3921,16 +3931,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115380340</t>
+          <t>https://artportalen.se/Sighting/115379346</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136202477</v>
+        <v>115380107</v>
       </c>
       <c r="B32" t="n">
-        <v>80559</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3958,17 +3968,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471221</v>
+        <v>471616</v>
       </c>
       <c r="R32" t="n">
-        <v>7142065</v>
+        <v>7141881</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3992,12 +4002,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4009,73 +4019,73 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AR32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202477</t>
+          <t>https://artportalen.se/Sighting/115380107</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89592266</v>
+        <v>115380340</v>
       </c>
       <c r="B33" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471260</v>
+        <v>471461</v>
       </c>
       <c r="R33" t="n">
-        <v>7141817</v>
+        <v>7141651</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4099,12 +4109,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,73 +4125,74 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Jennie Ramsell</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592266</t>
+          <t>https://artportalen.se/Sighting/115380340</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89592274</v>
+        <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80461</v>
+        <v>80559</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471395</v>
+        <v>471221</v>
       </c>
       <c r="R34" t="n">
-        <v>7141934</v>
+        <v>7142065</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4205,12 +4216,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4222,36 +4233,32 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+      <c r="AR34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SMF:s mykologivecka</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592274</t>
+          <t>https://artportalen.se/Sighting/136202477</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>89592341</v>
+        <v>89592266</v>
       </c>
       <c r="B35" t="n">
         <v>80461</v>
@@ -4286,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471235</v>
+        <v>471260</v>
       </c>
       <c r="R35" t="n">
-        <v>7141830</v>
+        <v>7141817</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,13 +4358,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592341</t>
+          <t>https://artportalen.se/Sighting/89592266</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89592353</v>
+        <v>89592274</v>
       </c>
       <c r="B36" t="n">
         <v>80461</v>
@@ -4392,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471289</v>
+        <v>471395</v>
       </c>
       <c r="R36" t="n">
-        <v>7142123</v>
+        <v>7141934</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4439,6 +4446,11 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -4457,38 +4469,38 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592353</t>
+          <t>https://artportalen.se/Sighting/89592274</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89592336</v>
+        <v>89592341</v>
       </c>
       <c r="B37" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4510,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471341</v>
+        <v>471235</v>
       </c>
       <c r="R37" t="n">
-        <v>7142128</v>
+        <v>7141830</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4536,11 +4548,6 @@
           <t>2020-08-27</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4568,54 +4575,54 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592336</t>
+          <t>https://artportalen.se/Sighting/89592341</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115380448</v>
+        <v>89592353</v>
       </c>
       <c r="B38" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Klingerhögtjärnen, Jmt</t>
+          <t>Medberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471496</v>
+        <v>471289</v>
       </c>
       <c r="R38" t="n">
-        <v>7141820</v>
+        <v>7142123</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4639,12 +4646,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4659,27 +4666,31 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115380448</t>
+          <t>https://artportalen.se/Sighting/89592353</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89592246</v>
+        <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>99140</v>
+        <v>80570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4687,37 +4698,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Medberget, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471436</v>
+        <v>471500</v>
       </c>
       <c r="R39" t="n">
-        <v>7141608</v>
+        <v>7141902</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4741,12 +4752,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4761,53 +4782,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592246</t>
+          <t>https://artportalen.se/Sighting/136195683</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89592293</v>
+        <v>89592336</v>
       </c>
       <c r="B40" t="n">
-        <v>80398</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4817,10 +4834,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471428</v>
+        <v>471341</v>
       </c>
       <c r="R40" t="n">
-        <v>7141774</v>
+        <v>7142128</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4855,6 +4872,11 @@
           <t>2020-08-27</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4882,49 +4904,54 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89592293</t>
+          <t>https://artportalen.se/Sighting/89592336</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136196765</v>
+        <v>115380448</v>
       </c>
       <c r="B41" t="n">
-        <v>79916</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6038705</v>
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kalberget mitten, Jmt</t>
+          <t>Klingerhögtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471210</v>
+        <v>471496</v>
       </c>
       <c r="R41" t="n">
-        <v>7141812</v>
+        <v>7141820</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,22 +4975,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,23 +4989,342 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo, Johan Råghall, Rashid Kadhim, Sten Svantesson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115380448</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>89592246</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>471436</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7141608</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592246</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>89592293</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Medberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>471428</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7141774</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592293</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136196765</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79916</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6038705</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cliostomum piceicola</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kalberget mitten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>471210</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7141812</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo, Johan Råghall, Rashid Kadhim, Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136196765</t>
         </is>
@@ -5036,6 +5372,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+          <t>Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79916</v>
+        <v>79917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79917</v>
+        <v>79921</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79921</v>
+        <v>79922</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79922</v>
+        <v>79926</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79926</v>
+        <v>79932</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83439</v>
+        <v>83452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79932</v>
+        <v>79945</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79945</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
